--- a/excel_config/indir/修炼方法.xlsx
+++ b/excel_config/indir/修炼方法.xlsx
@@ -5823,7 +5823,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>["method.hunyuan.1","method.hunyuan.2","method.hunyuan.3","method.hunyuan.4","method.hunyuan.5","method.hunyuan.6","method.hunyuan.7","method.hunyuan.8","method.hunyuan.9"]</t>
+          <t>method.hunyuan.1:method.hunyuan.2:method.hunyuan.3:method.hunyuan.4:method.hunyuan.5:method.hunyuan.6:method.hunyuan.7:method.hunyuan.8:method.hunyuan.9</t>
         </is>
       </c>
       <c r="F5" s="4" t="n"/>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>["method.changsheng.1","method.changsheng.2","method.changsheng.3","method.changsheng.4","method.changsheng.5","method.changsheng.6","method.changsheng.7","method.changsheng.8","method.changsheng.9"]</t>
+          <t>method.changsheng.1:method.changsheng.2:method.changsheng.3:method.changsheng.4:method.changsheng.5:method.changsheng.6:method.changsheng.7:method.changsheng.8:method.changsheng.9</t>
         </is>
       </c>
       <c r="F6" s="4" t="n"/>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>["method.taixu_sword.1","method.taixu_sword.2","method.taixu_sword.3","method.taixu_sword.4","method.taixu_sword.5","method.taixu_sword.6","method.taixu_sword.7","method.taixu_sword.8","method.taixu_sword.9"]</t>
+          <t>method.taixu_sword.1:method.taixu_sword.2:method.taixu_sword.3:method.taixu_sword.4:method.taixu_sword.5:method.taixu_sword.6:method.taixu_sword.7:method.taixu_sword.8:method.taixu_sword.9</t>
         </is>
       </c>
       <c r="F7" s="4" t="n"/>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>["method.vajra.1","method.vajra.2","method.vajra.3","method.vajra.4","method.vajra.5","method.vajra.6","method.vajra.7","method.vajra.8","method.vajra.9"]</t>
+          <t>method.vajra.1:method.vajra.2:method.vajra.3:method.vajra.4:method.vajra.5:method.vajra.6:method.vajra.7:method.vajra.8:method.vajra.9</t>
         </is>
       </c>
       <c r="F8" s="4" t="n"/>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>["method.taiyin.1","method.taiyin.2","method.taiyin.3","method.taiyin.4","method.taiyin.5","method.taiyin.6","method.taiyin.7","method.taiyin.8","method.taiyin.9"]</t>
+          <t>method.taiyin.1:method.taiyin.2:method.taiyin.3:method.taiyin.4:method.taiyin.5:method.taiyin.6:method.taiyin.7:method.taiyin.8:method.taiyin.9</t>
         </is>
       </c>
       <c r="F9" s="4" t="n"/>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>["method.leihuo.1","method.leihuo.2","method.leihuo.3","method.leihuo.4","method.leihuo.5","method.leihuo.6","method.leihuo.7","method.leihuo.8","method.leihuo.9"]</t>
+          <t>method.leihuo.1:method.leihuo.2:method.leihuo.3:method.leihuo.4:method.leihuo.5:method.leihuo.6:method.leihuo.7:method.leihuo.8:method.leihuo.9</t>
         </is>
       </c>
       <c r="F10" s="4" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>["method.zhoutian_craft.1","method.zhoutian_craft.2","method.zhoutian_craft.3","method.zhoutian_craft.4","method.zhoutian_craft.5","method.zhoutian_craft.6","method.zhoutian_craft.7","method.zhoutian_craft.8","method.zhoutian_craft.9"]</t>
+          <t>method.zhoutian_craft.1:method.zhoutian_craft.2:method.zhoutian_craft.3:method.zhoutian_craft.4:method.zhoutian_craft.5:method.zhoutian_craft.6:method.zhoutian_craft.7:method.zhoutian_craft.8:method.zhoutian_craft.9</t>
         </is>
       </c>
       <c r="F11" s="4" t="n"/>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>["method.wanxiang.1","method.wanxiang.2","method.wanxiang.3","method.wanxiang.4","method.wanxiang.5","method.wanxiang.6","method.wanxiang.7","method.wanxiang.8","method.wanxiang.9"]</t>
+          <t>method.wanxiang.1:method.wanxiang.2:method.wanxiang.3:method.wanxiang.4:method.wanxiang.5:method.wanxiang.6:method.wanxiang.7:method.wanxiang.8:method.wanxiang.9</t>
         </is>
       </c>
       <c r="F12" s="4" t="n"/>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>["method.jiuji.1","method.jiuji.2","method.jiuji.3","method.jiuji.4","method.jiuji.5"]</t>
+          <t>method.jiuji.1:method.jiuji.2:method.jiuji.3:method.jiuji.4:method.jiuji.5</t>
         </is>
       </c>
       <c r="F13" s="4" t="n"/>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>["method.blood_burst.1"]</t>
+          <t>method.blood_burst.1</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>["method.escape_art.1"]</t>
+          <t>method.escape_art.1</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>["method.poison_codex.1"]</t>
+          <t>method.poison_codex.1</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>["method.fate_gaze.1"]</t>
+          <t>method.fate_gaze.1</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>["method.talisman_archive.1"]</t>
+          <t>method.talisman_archive.1</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>["method.heavy_sword.1"]</t>
+          <t>method.heavy_sword.1</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -6623,42 +6623,42 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
     </row>
@@ -6728,11 +6728,7 @@
           <t>{"efficiency": 1, "deviationRisk": 0.07}</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "max_health", "base": 80, "operation": "add_flat", "stackGroup": "max_health", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 20}, {"effectId": "combat_mp_restore_2s", "base": 3, "operation": "add_flat", "stackGroup": "combat_mp_restore_2s", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "combat", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 2}, "masteryGrowth": 1}, {"effectId": "mana_regen", "base": 0.08, "operation": "add_percent", "stackGroup": "mana_regen", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.015}, {"effectId": "cultivation_speed", "base": 0.06, "operation": "add_percent", "stackGroup": "cultivation_speed", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 4}, "masteryGrowth": 0.03}]</t>
@@ -6744,21 +6740,9 @@
         </is>
       </c>
       <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
     </row>
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -6807,11 +6791,7 @@
           <t>{"efficiency": 1.12, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "max_mana", "base": 160, "operation": "add_flat", "stackGroup": "max_mana", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 35}, {"effectId": "cultivation_stability", "base": 0.12, "operation": "add_percent", "stackGroup": "cultivation_stability", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.02}, {"effectId": "deviation_resistance", "base": 0.12, "operation": "add_percent", "stackGroup": "deviation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.04}]</t>
@@ -6827,21 +6807,9 @@
           <t>{"predecessorId": "method.hunyuan.1", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
     </row>
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -6890,11 +6858,7 @@
           <t>{"efficiency": 1.24, "deviationRisk": 0.06}</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "max_mana", "base": 280, "operation": "add_flat", "stackGroup": "max_mana", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 55}, {"effectId": "all_spell_efficiency", "base": 0.08, "operation": "add_percent", "stackGroup": "all_spell_efficiency", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.015}, {"effectId": "breakthrough_success", "base": 0.08, "operation": "add_percent", "stackGroup": "breakthrough_success", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.03}]</t>
@@ -6910,21 +6874,9 @@
           <t>{"predecessorId": "method.hunyuan.2", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
     </row>
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -6973,11 +6925,7 @@
           <t>{"efficiency": 1.36, "deviationRisk": 0.055}</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "max_mana", "base": 430, "operation": "add_flat", "stackGroup": "max_mana", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 75}, {"effectId": "parallel_action_efficiency", "base": 0.06, "operation": "add_percent", "stackGroup": "parallel_action_efficiency", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.012}, {"effectId": "mana_control", "base": 0.14, "operation": "add_percent", "stackGroup": "mana_control", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.04}]</t>
@@ -6993,21 +6941,9 @@
           <t>{"predecessorId": "method.hunyuan.3", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
     </row>
     <row r="9" ht="27" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -7056,11 +6992,7 @@
           <t>{"efficiency": 1.48, "deviationRisk": 0.05}</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "mana_regen", "base": 0.22, "operation": "add_percent", "stackGroup": "mana_regen", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.025}, {"effectId": "domain_resistance", "base": 0.1, "operation": "add_percent", "stackGroup": "domain_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.018}, {"effectId": "ambient_qi_absorption", "base": 0.18, "operation": "add_percent", "stackGroup": "ambient_qi_absorption", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.05}]</t>
@@ -7076,21 +7008,9 @@
           <t>{"predecessorId": "method.hunyuan.4", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
     </row>
     <row r="10" ht="27" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -7139,11 +7059,7 @@
           <t>{"efficiency": 1.6, "deviationRisk": 0.045}</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "void_resistance", "base": 0.2, "operation": "add_percent", "stackGroup": "void_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.025}, {"effectId": "resource_conversion", "base": 0.12, "operation": "add_percent", "stackGroup": "resource_conversion", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.02}, {"effectId": "hostile_energy_conversion", "base": 0.16, "operation": "add_percent", "stackGroup": "hostile_energy_conversion", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.05}]</t>
@@ -7159,21 +7075,9 @@
           <t>{"predecessorId": "method.hunyuan.5", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
     </row>
     <row r="11" ht="27" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -7222,11 +7126,7 @@
           <t>{"efficiency": 1.72, "deviationRisk": 0.04}</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "max_mana", "base": 760, "operation": "add_flat", "stackGroup": "max_mana", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 120}, {"effectId": "all_efficiency", "base": 0.12, "operation": "add_percent", "stackGroup": "all_efficiency", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.02}, {"effectId": "sustained_cast_efficiency", "base": 0.22, "operation": "add_percent", "stackGroup": "sustained_cast_efficiency", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.06}]</t>
@@ -7242,21 +7142,9 @@
           <t>{"predecessorId": "method.hunyuan.6", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
     </row>
     <row r="12" ht="27" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -7305,11 +7193,7 @@
           <t>{"efficiency": 1.84, "deviationRisk": 0.035}</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "all_efficiency", "base": 0.2, "operation": "add_percent", "stackGroup": "all_efficiency", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.025}, {"effectId": "law_resistance", "base": 0.16, "operation": "add_percent", "stackGroup": "law_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.025}, {"effectId": "law_compatibility", "base": 0.2, "operation": "add_percent", "stackGroup": "law_compatibility", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.06}]</t>
@@ -7325,21 +7209,9 @@
           <t>{"predecessorId": "method.hunyuan.7", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
     </row>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -7384,14 +7256,10 @@
           <t>{"efficiency": 1.96, "deviationRisk": 0.03}</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"tribulation_resistance","base":0.24,"operation":"add_percent","stackGroup":"tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.03},{"effectId":"immortal_qi_conversion","base":0.22,"operation":"add_percent","stackGroup":"immortal_qi_conversion","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"cultivation","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.03},{"effectId":"ascension_stability","base":0.24,"operation":"add_percent","stackGroup":"ascension_stability","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.07}]</t>
+          <t>[{"effectId": "tribulation_resistance", "base": 0.24, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.03}, {"effectId": "immortal_qi_conversion", "base": 0.22, "operation": "add_percent", "stackGroup": "immortal_qi_conversion", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.03}, {"effectId": "ascension_stability", "base": 0.24, "operation": "add_percent", "stackGroup": "ascension_stability", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.07}]</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -7404,21 +7272,9 @@
           <t>{"predecessorId": "method.hunyuan.8", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -7463,11 +7319,7 @@
           <t>{"efficiency": 1, "deviationRisk": 0.07}</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "health_regen", "base": 0.1, "operation": "add_percent", "stackGroup": "health_regen", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.018}, {"effectId": "herb_yield", "base": 0.08, "operation": "add_percent", "stackGroup": "herb_yield", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.015}, {"effectId": "injury_recovery", "base": 0.1, "operation": "add_percent", "stackGroup": "injury_recovery", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.03}]</t>
@@ -7479,21 +7331,9 @@
         </is>
       </c>
       <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="3" t="n"/>
+      <c r="Q14" s="3" t="n"/>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -7542,11 +7382,7 @@
           <t>{"efficiency": 1.12, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "max_health", "base": 140, "operation": "add_flat", "stackGroup": "max_health", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 30}, {"effectId": "healing_power", "base": 0.1, "operation": "add_percent", "stackGroup": "healing_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.018}, {"effectId": "medicine_efficiency", "base": 0.14, "operation": "add_percent", "stackGroup": "medicine_efficiency", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.04}]</t>
@@ -7562,21 +7398,9 @@
           <t>{"predecessorId": "method.changsheng.1", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -7625,11 +7449,7 @@
           <t>{"efficiency": 1.24, "deviationRisk": 0.06}</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "healing_power", "base": 0.18, "operation": "add_percent", "stackGroup": "healing_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.022}, {"effectId": "poison_resistance", "base": 0.12, "operation": "add_percent", "stackGroup": "poison_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.018}, {"effectId": "bloodline_stability", "base": 0.16, "operation": "add_percent", "stackGroup": "bloodline_stability", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.05}]</t>
@@ -7645,21 +7465,9 @@
           <t>{"predecessorId": "method.changsheng.2", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="3" t="n"/>
+      <c r="Q16" s="3" t="n"/>
     </row>
     <row r="17" ht="27" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -7708,11 +7516,7 @@
           <t>{"efficiency": 1.36, "deviationRisk": 0.055}</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "soul_recovery", "base": 0.18, "operation": "add_percent", "stackGroup": "soul_recovery", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.025}, {"effectId": "health_regen", "base": 0.24, "operation": "add_percent", "stackGroup": "health_regen", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.025}, {"effectId": "soul_healing", "base": 0.18, "operation": "add_percent", "stackGroup": "soul_healing", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.05}]</t>
@@ -7728,21 +7532,9 @@
           <t>{"predecessorId": "method.changsheng.3", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -7791,11 +7583,7 @@
           <t>{"efficiency": 1.48, "deviationRisk": 0.05}</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "healing_power", "base": 0.3, "operation": "add_percent", "stackGroup": "healing_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.03}, {"effectId": "healing_domain", "base": 0.16, "operation": "add_percent", "stackGroup": "healing_domain", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "area", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.025}, {"effectId": "ally_healing", "base": 0.22, "operation": "add_percent", "stackGroup": "ally_healing", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "allies", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.06}]</t>
@@ -7811,21 +7599,9 @@
           <t>{"predecessorId": "method.changsheng.4", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="3" t="n"/>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -7874,11 +7650,7 @@
           <t>{"efficiency": 1.6, "deviationRisk": 0.045}</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "void_survival", "base": 0.24, "operation": "add_percent", "stackGroup": "void_survival", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.03}, {"effectId": "rare_herb_yield", "base": 0.18, "operation": "add_percent", "stackGroup": "rare_herb_yield", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.025}, {"effectId": "void_herb_growth", "base": 0.2, "operation": "add_percent", "stackGroup": "void_herb_growth", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.06}]</t>
@@ -7894,21 +7666,9 @@
           <t>{"predecessorId": "method.changsheng.5", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n"/>
     </row>
     <row r="20" ht="27" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -7957,11 +7717,7 @@
           <t>{"efficiency": 1.72, "deviationRisk": 0.04}</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "pill_quality", "base": 0.24, "operation": "add_percent", "stackGroup": "pill_quality", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.03}, {"effectId": "max_health", "base": 520, "operation": "add_flat", "stackGroup": "max_health", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 2}, "masteryGrowth": 85}, {"effectId": "alchemy_success", "base": 0.24, "operation": "add_percent", "stackGroup": "alchemy_success", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.06}]</t>
@@ -7977,21 +7733,9 @@
           <t>{"predecessorId": "method.changsheng.6", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n"/>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -8040,11 +7784,7 @@
           <t>{"efficiency": 1.84, "deviationRisk": 0.035}</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "fatal_recovery_chance", "base": 0.12, "operation": "add_percent", "stackGroup": "fatal_recovery_chance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.018}, {"effectId": "lifespan_efficiency", "base": 0.22, "operation": "add_percent", "stackGroup": "lifespan_efficiency", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.03}, {"effectId": "resurrection_cost_reduction", "base": 0.22, "operation": "add_percent", "stackGroup": "resurrection_cost_reduction", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.07}]</t>
@@ -8060,21 +7800,9 @@
           <t>{"predecessorId": "method.changsheng.7", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
     </row>
     <row r="22" ht="27" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -8119,11 +7847,7 @@
           <t>{"efficiency": 1.96, "deviationRisk": 0.03}</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "tribulation_recovery", "base": 0.28, "operation": "add_percent", "stackGroup": "tribulation_recovery", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.035}, {"effectId": "tribulation_resistance", "base": 0.14, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.025}, {"effectId": "pill_tribulation_resistance", "base": 0.28, "operation": "add_percent", "stackGroup": "pill_tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.08}]</t>
@@ -8139,21 +7863,9 @@
           <t>{"predecessorId": "method.changsheng.8", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="n"/>
+      <c r="Q22" s="3" t="n"/>
     </row>
     <row r="23" ht="27" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -8198,11 +7910,7 @@
           <t>{"efficiency": 1.04, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "sword_damage", "base": 0.132, "operation": "add_percent", "stackGroup": "sword_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.022}, {"effectId": "sword_control", "base": 0.11, "operation": "add_percent", "stackGroup": "sword_control", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.02}, {"effectId": "sword_attack_speed", "base": 0.088, "operation": "add_percent", "stackGroup": "sword_attack_speed", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.033}]</t>
@@ -8214,21 +7922,9 @@
         </is>
       </c>
       <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
     </row>
     <row r="24" ht="27" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -8277,11 +7973,7 @@
           <t>{"efficiency": 1.16, "deviationRisk": 0.06}</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "damage_bonus", "base": 0.088, "operation": "add_percent", "stackGroup": "damage_bonus", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.015}, {"effectId": "sword_damage", "base": 0.198, "operation": "add_percent", "stackGroup": "sword_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.024}, {"effectId": "sword_intent_power", "base": 0.154, "operation": "add_percent", "stackGroup": "sword_intent_power", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.044}]</t>
@@ -8297,21 +7989,9 @@
           <t>{"predecessorId": "method.taixu_sword.1", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O24" s="3" t="n"/>
+      <c r="P24" s="3" t="n"/>
+      <c r="Q24" s="3" t="n"/>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -8360,11 +8040,7 @@
           <t>{"efficiency": 1.28, "deviationRisk": 0.055}</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "multi_sword_count", "base": 2.2, "operation": "add_flat", "stackGroup": "multi_sword_count", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 1.1}, {"effectId": "formation_damage", "base": 0.154, "operation": "add_percent", "stackGroup": "formation_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.022}, {"effectId": "sword_formation_control", "base": 0.176, "operation": "add_percent", "stackGroup": "sword_formation_control", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.055}]</t>
@@ -8380,21 +8056,9 @@
           <t>{"predecessorId": "method.taixu_sword.2", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n"/>
+      <c r="Q25" s="3" t="n"/>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -8443,11 +8107,7 @@
           <t>{"efficiency": 1.4, "deviationRisk": 0.05}</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "armor_pierce", "base": 0.176, "operation": "add_percent", "stackGroup": "armor_pierce", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.024}, {"effectId": "remote_control_range", "base": 0.22, "operation": "add_percent", "stackGroup": "remote_control_range", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.033}, {"effectId": "weakness_detection", "base": 0.198, "operation": "add_percent", "stackGroup": "weakness_detection", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.055}]</t>
@@ -8463,21 +8123,9 @@
           <t>{"predecessorId": "method.taixu_sword.3", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="3" t="n"/>
+      <c r="Q26" s="3" t="n"/>
     </row>
     <row r="27" ht="27" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -8526,11 +8174,7 @@
           <t>{"efficiency": 1.52, "deviationRisk": 0.045}</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "sword_domain", "base": 0.264, "operation": "add_percent", "stackGroup": "sword_domain", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "area", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.033}, {"effectId": "spell_suppression", "base": 0.132, "operation": "add_percent", "stackGroup": "spell_suppression", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.022}, {"effectId": "domain_range", "base": 0.22, "operation": "add_percent", "stackGroup": "domain_range", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.066}]</t>
@@ -8546,21 +8190,9 @@
           <t>{"predecessorId": "method.taixu_sword.4", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
     </row>
     <row r="28" ht="27" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -8609,11 +8241,7 @@
           <t>{"efficiency": 1.64, "deviationRisk": 0.04}</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "space_pierce", "base": 0.242, "operation": "add_percent", "stackGroup": "space_pierce", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.033}, {"effectId": "sword_damage", "base": 0.374, "operation": "add_percent", "stackGroup": "sword_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.039}, {"effectId": "void_target_accuracy", "base": 0.242, "operation": "add_percent", "stackGroup": "void_target_accuracy", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.066}]</t>
@@ -8629,21 +8257,9 @@
           <t>{"predecessorId": "method.taixu_sword.5", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="3" t="n"/>
+      <c r="Q28" s="3" t="n"/>
     </row>
     <row r="29" ht="27" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -8692,11 +8308,7 @@
           <t>{"efficiency": 1.76, "deviationRisk": 0.035}</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "sword_damage", "base": 0.462, "operation": "add_percent", "stackGroup": "sword_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.044}, {"effectId": "weapon_loss_resistance", "base": 0.33, "operation": "add_percent", "stackGroup": "weapon_loss_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.044}, {"effectId": "life_bound_sync", "base": 0.275, "operation": "add_percent", "stackGroup": "life_bound_sync", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.077}]</t>
@@ -8712,21 +8324,9 @@
           <t>{"predecessorId": "method.taixu_sword.6", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="3" t="n"/>
+      <c r="Q29" s="3" t="n"/>
     </row>
     <row r="30" ht="27" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -8775,11 +8375,7 @@
           <t>{"efficiency": 1.88, "deviationRisk": 0.03}</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K30" s="3" t="n"/>
       <c r="L30" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "law_pierce", "base": 0.286, "operation": "add_percent", "stackGroup": "law_pierce", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.039}, {"effectId": "sword_damage", "base": 0.616, "operation": "add_percent", "stackGroup": "sword_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.05}, {"effectId": "dao_sword_power", "base": 0.308, "operation": "add_percent", "stackGroup": "dao_sword_power", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.088}]</t>
@@ -8795,21 +8391,9 @@
           <t>{"predecessorId": "method.taixu_sword.7", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="3" t="n"/>
+      <c r="Q30" s="3" t="n"/>
     </row>
     <row r="31" ht="27" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -8854,11 +8438,7 @@
           <t>{"efficiency": 2, "deviationRisk": 0.025}</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "tribulation_damage", "base": 0.44, "operation": "add_percent", "stackGroup": "tribulation_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.055}, {"effectId": "law_pierce", "base": 0.418, "operation": "add_percent", "stackGroup": "law_pierce", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.05}, {"effectId": "tribulation_sever", "base": 0.352, "operation": "add_percent", "stackGroup": "tribulation_sever", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.099}]</t>
@@ -8874,21 +8454,9 @@
           <t>{"predecessorId": "method.taixu_sword.8", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="3" t="n"/>
+      <c r="Q31" s="3" t="n"/>
     </row>
     <row r="32" ht="27" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -8933,11 +8501,7 @@
           <t>{"efficiency": 1, "deviationRisk": 0.07}</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "max_health", "base": 120, "operation": "add_flat", "stackGroup": "max_health", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 25}, {"effectId": "physical_resistance", "base": 0.08, "operation": "add_percent", "stackGroup": "physical_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.015}, {"effectId": "stamina", "base": 0.1, "operation": "add_percent", "stackGroup": "stamina", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.03}]</t>
@@ -8949,21 +8513,9 @@
         </is>
       </c>
       <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O32" s="3" t="n"/>
+      <c r="P32" s="3" t="n"/>
+      <c r="Q32" s="3" t="n"/>
     </row>
     <row r="33" ht="27" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -9012,11 +8564,7 @@
           <t>{"efficiency": 1.12, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "max_health", "base": 240, "operation": "add_flat", "stackGroup": "max_health", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 45}, {"effectId": "spiritual_resistance", "base": 0.1, "operation": "add_percent", "stackGroup": "spiritual_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.018}, {"effectId": "stagger_resistance", "base": 0.14, "operation": "add_percent", "stackGroup": "stagger_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.04}]</t>
@@ -9032,21 +8580,9 @@
           <t>{"predecessorId": "method.vajra.1", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="n"/>
     </row>
     <row r="34" ht="27" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -9095,11 +8631,7 @@
           <t>{"efficiency": 1.24, "deviationRisk": 0.06}</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "max_health", "base": 380, "operation": "add_flat", "stackGroup": "max_health", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 65}, {"effectId": "melee_damage", "base": 0.15, "operation": "add_percent", "stackGroup": "melee_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.022}, {"effectId": "bloodline_output", "base": 0.16, "operation": "add_percent", "stackGroup": "bloodline_output", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.05}]</t>
@@ -9115,21 +8647,9 @@
           <t>{"predecessorId": "method.vajra.2", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="3" t="n"/>
+      <c r="Q34" s="3" t="n"/>
     </row>
     <row r="35" ht="27" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -9178,11 +8698,7 @@
           <t>{"efficiency": 1.36, "deviationRisk": 0.055}</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K35" s="3" t="n"/>
       <c r="L35" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "health_regen", "base": 0.22, "operation": "add_percent", "stackGroup": "health_regen", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.03}, {"effectId": "fatal_resistance", "base": 0.1, "operation": "add_percent", "stackGroup": "fatal_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.018}, {"effectId": "regeneration_speed", "base": 0.18, "operation": "add_percent", "stackGroup": "regeneration_speed", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.05}]</t>
@@ -9198,21 +8714,9 @@
           <t>{"predecessorId": "method.vajra.3", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="3" t="n"/>
+      <c r="Q35" s="3" t="n"/>
     </row>
     <row r="36" ht="27" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
@@ -9261,11 +8765,7 @@
           <t>{"efficiency": 1.48, "deviationRisk": 0.05}</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "melee_damage", "base": 0.3, "operation": "add_percent", "stackGroup": "melee_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.035}, {"effectId": "max_health", "base": 620, "operation": "add_flat", "stackGroup": "max_health", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 2}, "masteryGrowth": 90}, {"effectId": "dharma_form_power", "base": 0.22, "operation": "add_percent", "stackGroup": "dharma_form_power", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.06}]</t>
@@ -9281,21 +8781,9 @@
           <t>{"predecessorId": "method.vajra.4", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O36" s="3" t="n"/>
+      <c r="P36" s="3" t="n"/>
+      <c r="Q36" s="3" t="n"/>
     </row>
     <row r="37" ht="27" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -9344,11 +8832,7 @@
           <t>{"efficiency": 1.6, "deviationRisk": 0.045}</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "void_resistance", "base": 0.3, "operation": "add_percent", "stackGroup": "void_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.035}, {"effectId": "max_health", "base": 800, "operation": "add_flat", "stackGroup": "max_health", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 2}, "masteryGrowth": 110}, {"effectId": "void_mobility", "base": 0.2, "operation": "add_percent", "stackGroup": "void_mobility", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.06}]</t>
@@ -9364,21 +8848,9 @@
           <t>{"predecessorId": "method.vajra.5", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O37" s="3" t="n"/>
+      <c r="P37" s="3" t="n"/>
+      <c r="Q37" s="3" t="n"/>
     </row>
     <row r="38" ht="27" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -9427,11 +8899,7 @@
           <t>{"efficiency": 1.72, "deviationRisk": 0.04}</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "all_resistance", "base": 0.18, "operation": "add_percent", "stackGroup": "all_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.025}, {"effectId": "melee_damage", "base": 0.38, "operation": "add_percent", "stackGroup": "melee_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.04}, {"effectId": "body_energy_efficiency", "base": 0.24, "operation": "add_percent", "stackGroup": "body_energy_efficiency", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.07}]</t>
@@ -9447,21 +8915,9 @@
           <t>{"predecessorId": "method.vajra.6", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O38" s="3" t="n"/>
+      <c r="P38" s="3" t="n"/>
+      <c r="Q38" s="3" t="n"/>
     </row>
     <row r="39" ht="27" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -9510,11 +8966,7 @@
           <t>{"efficiency": 1.84, "deviationRisk": 0.035}</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "fatal_resistance", "base": 0.25, "operation": "add_percent", "stackGroup": "fatal_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.03}, {"effectId": "max_health", "base": 1250, "operation": "add_flat", "stackGroup": "max_health", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 2}, "masteryGrowth": 150}, {"effectId": "immortal_recovery", "base": 0.26, "operation": "add_percent", "stackGroup": "immortal_recovery", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.08}]</t>
@@ -9530,21 +8982,9 @@
           <t>{"predecessorId": "method.vajra.7", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
+      <c r="Q39" s="3" t="n"/>
     </row>
     <row r="40" ht="27" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -9589,14 +9029,10 @@
           <t>{"efficiency": 1.96, "deviationRisk": 0.03}</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"tribulation_resistance","base":0.4,"operation":"add_percent","stackGroup":"tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.045},{"effectId":"all_resistance","base":0.28,"operation":"add_percent","stackGroup":"all_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.035},{"effectId":"tribulation_energy_absorption","base":0.3,"operation":"add_percent","stackGroup":"tribulation_energy_absorption","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.09}]</t>
+          <t>[{"effectId": "tribulation_resistance", "base": 0.4, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.045}, {"effectId": "all_resistance", "base": 0.28, "operation": "add_percent", "stackGroup": "all_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.035}, {"effectId": "tribulation_energy_absorption", "base": 0.3, "operation": "add_percent", "stackGroup": "tribulation_energy_absorption", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.09}]</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -9609,21 +9045,9 @@
           <t>{"predecessorId": "method.vajra.8", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O40" s="3" t="n"/>
+      <c r="P40" s="3" t="n"/>
+      <c r="Q40" s="3" t="n"/>
     </row>
     <row r="41" ht="27" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -9668,11 +9092,7 @@
           <t>{"efficiency": 1.04, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K41" s="3" t="n"/>
       <c r="L41" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "spirit_power", "base": 0.132, "operation": "add_percent", "stackGroup": "spirit_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.022}, {"effectId": "mental_resistance", "base": 0.11, "operation": "add_percent", "stackGroup": "mental_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.02}, {"effectId": "spirit_sense_range", "base": 0.11, "operation": "add_percent", "stackGroup": "spirit_sense_range", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.033}]</t>
@@ -9684,21 +9104,9 @@
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="3" t="n"/>
+      <c r="Q41" s="3" t="n"/>
     </row>
     <row r="42" ht="27" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -9747,11 +9155,7 @@
           <t>{"efficiency": 1.16, "deviationRisk": 0.06}</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K42" s="3" t="n"/>
       <c r="L42" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "mental_resistance", "base": 0.22, "operation": "add_percent", "stackGroup": "mental_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.028}, {"effectId": "seal_power", "base": 0.11, "operation": "add_percent", "stackGroup": "seal_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.02}, {"effectId": "inner_demon_resistance", "base": 0.154, "operation": "add_percent", "stackGroup": "inner_demon_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.044}]</t>
@@ -9767,21 +9171,9 @@
           <t>{"predecessorId": "method.taiyin.1", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O42" s="3" t="n"/>
+      <c r="P42" s="3" t="n"/>
+      <c r="Q42" s="3" t="n"/>
     </row>
     <row r="43" ht="27" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -9830,11 +9222,7 @@
           <t>{"efficiency": 1.28, "deviationRisk": 0.055}</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K43" s="3" t="n"/>
       <c r="L43" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "soul_resistance", "base": 0.264, "operation": "add_percent", "stackGroup": "soul_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.033}, {"effectId": "curse_power", "base": 0.132, "operation": "add_percent", "stackGroup": "curse_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.022}, {"effectId": "curse_resistance", "base": 0.176, "operation": "add_percent", "stackGroup": "curse_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.055}]</t>
@@ -9850,21 +9238,9 @@
           <t>{"predecessorId": "method.taiyin.2", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O43" s="3" t="n"/>
+      <c r="P43" s="3" t="n"/>
+      <c r="Q43" s="3" t="n"/>
     </row>
     <row r="44" ht="27" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
@@ -9913,11 +9289,7 @@
           <t>{"efficiency": 1.4, "deviationRisk": 0.05}</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "parallel_action_efficiency", "base": 0.198, "operation": "add_percent", "stackGroup": "parallel_action_efficiency", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.028}, {"effectId": "contract_power", "base": 0.154, "operation": "add_percent", "stackGroup": "contract_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.024}, {"effectId": "split_mind_capacity", "base": 1.1, "operation": "add_flat", "stackGroup": "split_mind_capacity", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 3}, "masteryGrowth": 1.1}]</t>
@@ -9933,21 +9305,9 @@
           <t>{"predecessorId": "method.taiyin.3", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O44" s="3" t="n"/>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
     </row>
     <row r="45" ht="27" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -9996,11 +9356,7 @@
           <t>{"efficiency": 1.52, "deviationRisk": 0.045}</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K45" s="3" t="n"/>
       <c r="L45" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "spirit_power", "base": 0.33, "operation": "add_percent", "stackGroup": "spirit_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.039}, {"effectId": "dream_power", "base": 0.22, "operation": "add_percent", "stackGroup": "dream_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.033}, {"effectId": "dream_infiltration", "base": 0.242, "operation": "add_percent", "stackGroup": "dream_infiltration", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.066}]</t>
@@ -10016,21 +9372,9 @@
           <t>{"predecessorId": "method.taiyin.4", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O45" s="3" t="n"/>
+      <c r="P45" s="3" t="n"/>
+      <c r="Q45" s="3" t="n"/>
     </row>
     <row r="46" ht="27" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
@@ -10079,11 +9423,7 @@
           <t>{"efficiency": 1.64, "deviationRisk": 0.04}</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "spirit_power", "base": 0.462, "operation": "add_percent", "stackGroup": "spirit_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.044}, {"effectId": "true_name_power", "base": 0.22, "operation": "add_percent", "stackGroup": "true_name_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.033}, {"effectId": "true_name_accuracy", "base": 0.242, "operation": "add_percent", "stackGroup": "true_name_accuracy", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.066}]</t>
@@ -10099,21 +9439,9 @@
           <t>{"predecessorId": "method.taiyin.5", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="3" t="n"/>
+      <c r="Q46" s="3" t="n"/>
     </row>
     <row r="47" ht="27" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -10162,14 +9490,10 @@
           <t>{"efficiency": 1.76, "deviationRisk": 0.035}</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K47" s="3" t="n"/>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"mental_resistance","base":0.396,"operation":"add_percent","stackGroup":"mental_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.044},{"effectId":"causality_resistance","base":0.22,"operation":"add_percent","stackGroup":"causality_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.033},{"effectId":"causality_detection","base":0.264,"operation":"add_percent","stackGroup":"causality_detection","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.077}]</t>
+          <t>[{"effectId": "mental_resistance", "base": 0.396, "operation": "add_percent", "stackGroup": "mental_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.044}, {"effectId": "causality_resistance", "base": 0.22, "operation": "add_percent", "stackGroup": "causality_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.033}, {"effectId": "causality_detection", "base": 0.264, "operation": "add_percent", "stackGroup": "causality_detection", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.077}]</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -10182,21 +9506,9 @@
           <t>{"predecessorId": "method.taiyin.6", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O47" s="3" t="n"/>
+      <c r="P47" s="3" t="n"/>
+      <c r="Q47" s="3" t="n"/>
     </row>
     <row r="48" ht="27" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
@@ -10245,11 +9557,7 @@
           <t>{"efficiency": 1.88, "deviationRisk": 0.03}</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K48" s="3" t="n"/>
       <c r="L48" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "mental_resistance", "base": 0.55, "operation": "add_percent", "stackGroup": "mental_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.055}, {"effectId": "decree_power", "base": 0.286, "operation": "add_percent", "stackGroup": "decree_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.039}, {"effectId": "dao_heart_stability", "base": 0.308, "operation": "add_percent", "stackGroup": "dao_heart_stability", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.088}]</t>
@@ -10265,21 +9573,9 @@
           <t>{"predecessorId": "method.taiyin.7", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q48" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O48" s="3" t="n"/>
+      <c r="P48" s="3" t="n"/>
+      <c r="Q48" s="3" t="n"/>
     </row>
     <row r="49" ht="27" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
@@ -10324,14 +9620,10 @@
           <t>{"efficiency": 2, "deviationRisk": 0.025}</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K49" s="3" t="n"/>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"heart_tribulation_resistance","base":0.55,"operation":"add_percent","stackGroup":"heart_tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.055},{"effectId":"tribulation_control","base":0.242,"operation":"add_percent","stackGroup":"tribulation_control","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"control","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.039},{"effectId":"heart_tribulation_insight","base":0.352,"operation":"add_percent","stackGroup":"heart_tribulation_insight","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.099}]</t>
+          <t>[{"effectId": "heart_tribulation_resistance", "base": 0.55, "operation": "add_percent", "stackGroup": "heart_tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.055}, {"effectId": "tribulation_control", "base": 0.242, "operation": "add_percent", "stackGroup": "tribulation_control", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.039}, {"effectId": "heart_tribulation_insight", "base": 0.352, "operation": "add_percent", "stackGroup": "heart_tribulation_insight", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.099}]</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -10344,21 +9636,9 @@
           <t>{"predecessorId": "method.taiyin.8", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q49" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O49" s="3" t="n"/>
+      <c r="P49" s="3" t="n"/>
+      <c r="Q49" s="3" t="n"/>
     </row>
     <row r="50" ht="27" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
@@ -10403,11 +9683,7 @@
           <t>{"efficiency": 1.04, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K50" s="3" t="n"/>
       <c r="L50" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "spell_damage", "base": 0.154, "operation": "add_percent", "stackGroup": "spell_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.024}, {"effectId": "element_control", "base": 0.11, "operation": "add_percent", "stackGroup": "element_control", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.02}, {"effectId": "cast_speed", "base": 0.088, "operation": "add_percent", "stackGroup": "cast_speed", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.033}]</t>
@@ -10419,21 +9695,9 @@
         </is>
       </c>
       <c r="N50" s="3" t="n"/>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P50" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q50" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O50" s="3" t="n"/>
+      <c r="P50" s="3" t="n"/>
+      <c r="Q50" s="3" t="n"/>
     </row>
     <row r="51" ht="27" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -10482,11 +9746,7 @@
           <t>{"efficiency": 1.16, "deviationRisk": 0.06}</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K51" s="3" t="n"/>
       <c r="L51" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "spell_damage", "base": 0.242, "operation": "add_percent", "stackGroup": "spell_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.031}, {"effectId": "mana_efficiency", "base": 0.11, "operation": "add_percent", "stackGroup": "mana_efficiency", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.02}, {"effectId": "element_conversion", "base": 0.154, "operation": "add_percent", "stackGroup": "element_conversion", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.044}]</t>
@@ -10502,21 +9762,9 @@
           <t>{"predecessorId": "method.leihuo.1", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q51" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O51" s="3" t="n"/>
+      <c r="P51" s="3" t="n"/>
+      <c r="Q51" s="3" t="n"/>
     </row>
     <row r="52" ht="27" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
@@ -10565,11 +9813,7 @@
           <t>{"efficiency": 1.28, "deviationRisk": 0.055}</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K52" s="3" t="n"/>
       <c r="L52" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "thunder_damage", "base": 0.33, "operation": "add_percent", "stackGroup": "thunder_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.039}, {"effectId": "evil_bane", "base": 0.176, "operation": "add_percent", "stackGroup": "evil_bane", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.028}, {"effectId": "lightning_chain_count", "base": 1.1, "operation": "add_flat", "stackGroup": "lightning_chain_count", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 3}, "masteryGrowth": 1.1}]</t>
@@ -10585,21 +9829,9 @@
           <t>{"predecessorId": "method.leihuo.2", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P52" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q52" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O52" s="3" t="n"/>
+      <c r="P52" s="3" t="n"/>
+      <c r="Q52" s="3" t="n"/>
     </row>
     <row r="53" ht="27" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
@@ -10648,11 +9880,7 @@
           <t>{"efficiency": 1.4, "deviationRisk": 0.05}</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K53" s="3" t="n"/>
       <c r="L53" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "spell_damage", "base": 0.374, "operation": "add_percent", "stackGroup": "spell_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.042}, {"effectId": "weather_control", "base": 0.132, "operation": "add_percent", "stackGroup": "weather_control", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "area", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.022}, {"effectId": "environment_spell_bonus", "base": 0.198, "operation": "add_percent", "stackGroup": "environment_spell_bonus", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.055}]</t>
@@ -10668,21 +9896,9 @@
           <t>{"predecessorId": "method.leihuo.3", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P53" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q53" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O53" s="3" t="n"/>
+      <c r="P53" s="3" t="n"/>
+      <c r="Q53" s="3" t="n"/>
     </row>
     <row r="54" ht="27" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
@@ -10731,11 +9947,7 @@
           <t>{"efficiency": 1.52, "deviationRisk": 0.045}</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K54" s="3" t="n"/>
       <c r="L54" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "spell_domain", "base": 0.33, "operation": "add_percent", "stackGroup": "spell_domain", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "area", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.039}, {"effectId": "thunder_damage", "base": 0.44, "operation": "add_percent", "stackGroup": "thunder_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.044}, {"effectId": "domain_damage", "base": 0.242, "operation": "add_percent", "stackGroup": "domain_damage", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "area", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.066}]</t>
@@ -10751,21 +9963,9 @@
           <t>{"predecessorId": "method.leihuo.4", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q54" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O54" s="3" t="n"/>
+      <c r="P54" s="3" t="n"/>
+      <c r="Q54" s="3" t="n"/>
     </row>
     <row r="55" ht="27" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -10814,11 +10014,7 @@
           <t>{"efficiency": 1.64, "deviationRisk": 0.04}</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K55" s="3" t="n"/>
       <c r="L55" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "space_pierce", "base": 0.22, "operation": "add_percent", "stackGroup": "space_pierce", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.033}, {"effectId": "spell_damage", "base": 0.55, "operation": "add_percent", "stackGroup": "spell_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.05}, {"effectId": "void_spell_accuracy", "base": 0.242, "operation": "add_percent", "stackGroup": "void_spell_accuracy", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.066}]</t>
@@ -10834,21 +10030,9 @@
           <t>{"predecessorId": "method.leihuo.5", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q55" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O55" s="3" t="n"/>
+      <c r="P55" s="3" t="n"/>
+      <c r="Q55" s="3" t="n"/>
     </row>
     <row r="56" ht="27" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
@@ -10897,14 +10081,10 @@
           <t>{"efficiency": 1.76, "deviationRisk": 0.035}</t>
         </is>
       </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K56" s="3" t="n"/>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"law_spell_power","base":0.352,"operation":"add_percent","stackGroup":"law_spell_power","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.044},{"effectId":"thunder_damage","base":0.638,"operation":"add_percent","stackGroup":"thunder_damage","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"offense","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.055},{"effectId":"law_spell_efficiency","base":0.275,"operation":"add_percent","stackGroup":"law_spell_efficiency","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.077}]</t>
+          <t>[{"effectId": "law_spell_power", "base": 0.352, "operation": "add_percent", "stackGroup": "law_spell_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.044}, {"effectId": "thunder_damage", "base": 0.638, "operation": "add_percent", "stackGroup": "thunder_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.055}, {"effectId": "law_spell_efficiency", "base": 0.275, "operation": "add_percent", "stackGroup": "law_spell_efficiency", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.077}]</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -10917,21 +10097,9 @@
           <t>{"predecessorId": "method.leihuo.6", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q56" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O56" s="3" t="n"/>
+      <c r="P56" s="3" t="n"/>
+      <c r="Q56" s="3" t="n"/>
     </row>
     <row r="57" ht="27" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
@@ -10980,11 +10148,7 @@
           <t>{"efficiency": 1.88, "deviationRisk": 0.03}</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K57" s="3" t="n"/>
       <c r="L57" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "world_spell_power", "base": 0.44, "operation": "add_percent", "stackGroup": "world_spell_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.05}, {"effectId": "spell_domain", "base": 0.462, "operation": "add_percent", "stackGroup": "spell_domain", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "area", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.05}, {"effectId": "world_spell_duration", "base": 0.308, "operation": "add_percent", "stackGroup": "world_spell_duration", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.088}]</t>
@@ -11000,21 +10164,9 @@
           <t>{"predecessorId": "method.leihuo.7", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P57" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q57" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O57" s="3" t="n"/>
+      <c r="P57" s="3" t="n"/>
+      <c r="Q57" s="3" t="n"/>
     </row>
     <row r="58" ht="27" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
@@ -11059,14 +10211,10 @@
           <t>{"efficiency": 2, "deviationRisk": 0.025}</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K58" s="3" t="n"/>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"tribulation_damage","base":0.605,"operation":"add_percent","stackGroup":"tribulation_damage","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"offense","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.061},{"effectId":"tribulation_resistance","base":0.22,"operation":"add_percent","stackGroup":"tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.033},{"effectId":"tribulation_energy_absorption","base":0.33,"operation":"add_percent","stackGroup":"tribulation_energy_absorption","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.099}]</t>
+          <t>[{"effectId": "tribulation_damage", "base": 0.605, "operation": "add_percent", "stackGroup": "tribulation_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.061}, {"effectId": "tribulation_resistance", "base": 0.22, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.033}, {"effectId": "tribulation_energy_absorption", "base": 0.33, "operation": "add_percent", "stackGroup": "tribulation_energy_absorption", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.099}]</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -11079,21 +10227,9 @@
           <t>{"predecessorId": "method.leihuo.8", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q58" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O58" s="3" t="n"/>
+      <c r="P58" s="3" t="n"/>
+      <c r="Q58" s="3" t="n"/>
     </row>
     <row r="59" ht="27" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
@@ -11138,11 +10274,7 @@
           <t>{"efficiency": 1, "deviationRisk": 0.07}</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K59" s="3" t="n"/>
       <c r="L59" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "craft_quality", "base": 0.1, "operation": "add_percent", "stackGroup": "craft_quality", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.018}, {"effectId": "formation_power", "base": 0.08, "operation": "add_percent", "stackGroup": "formation_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.015}, {"effectId": "material_efficiency", "base": 0.1, "operation": "add_percent", "stackGroup": "material_efficiency", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.03}]</t>
@@ -11154,21 +10286,9 @@
         </is>
       </c>
       <c r="N59" s="3" t="n"/>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q59" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O59" s="3" t="n"/>
+      <c r="P59" s="3" t="n"/>
+      <c r="Q59" s="3" t="n"/>
     </row>
     <row r="60" ht="27" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
@@ -11217,11 +10337,7 @@
           <t>{"efficiency": 1.12, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K60" s="3" t="n"/>
       <c r="L60" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "craft_quality", "base": 0.18, "operation": "add_percent", "stackGroup": "craft_quality", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.025}, {"effectId": "formation_power", "base": 0.16, "operation": "add_percent", "stackGroup": "formation_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.022}, {"effectId": "inscription_success", "base": 0.14, "operation": "add_percent", "stackGroup": "inscription_success", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.04}]</t>
@@ -11237,21 +10353,9 @@
           <t>{"predecessorId": "method.zhoutian_craft.1", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q60" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O60" s="3" t="n"/>
+      <c r="P60" s="3" t="n"/>
+      <c r="Q60" s="3" t="n"/>
     </row>
     <row r="61" ht="27" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
@@ -11300,11 +10404,7 @@
           <t>{"efficiency": 1.24, "deviationRisk": 0.06}</t>
         </is>
       </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K61" s="3" t="n"/>
       <c r="L61" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "artifact_power", "base": 0.22, "operation": "add_percent", "stackGroup": "artifact_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.03}, {"effectId": "puppet_power", "base": 0.16, "operation": "add_percent", "stackGroup": "puppet_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.025}, {"effectId": "puppet_capacity", "base": 1, "operation": "add_flat", "stackGroup": "puppet_capacity", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "flat", "displayPriority": 3}, "masteryGrowth": 1}]</t>
@@ -11320,21 +10420,9 @@
           <t>{"predecessorId": "method.zhoutian_craft.2", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q61" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O61" s="3" t="n"/>
+      <c r="P61" s="3" t="n"/>
+      <c r="Q61" s="3" t="n"/>
     </row>
     <row r="62" ht="27" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
@@ -11383,11 +10471,7 @@
           <t>{"efficiency": 1.36, "deviationRisk": 0.055}</t>
         </is>
       </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K62" s="3" t="n"/>
       <c r="L62" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "artifact_power", "base": 0.3, "operation": "add_percent", "stackGroup": "artifact_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.035}, {"effectId": "teleport_stability", "base": 0.2, "operation": "add_percent", "stackGroup": "teleport_stability", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.03}, {"effectId": "life_bound_sync", "base": 0.18, "operation": "add_percent", "stackGroup": "life_bound_sync", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.05}]</t>
@@ -11403,21 +10487,9 @@
           <t>{"predecessorId": "method.zhoutian_craft.3", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q62" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O62" s="3" t="n"/>
+      <c r="P62" s="3" t="n"/>
+      <c r="Q62" s="3" t="n"/>
     </row>
     <row r="63" ht="27" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
@@ -11466,11 +10538,7 @@
           <t>{"efficiency": 1.48, "deviationRisk": 0.05}</t>
         </is>
       </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K63" s="3" t="n"/>
       <c r="L63" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "artifact_power", "base": 0.38, "operation": "add_percent", "stackGroup": "artifact_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.04}, {"effectId": "formation_power", "base": 0.3, "operation": "add_percent", "stackGroup": "formation_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.035}, {"effectId": "artifact_autonomy", "base": 0.22, "operation": "add_percent", "stackGroup": "artifact_autonomy", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.06}]</t>
@@ -11486,21 +10554,9 @@
           <t>{"predecessorId": "method.zhoutian_craft.4", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q63" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O63" s="3" t="n"/>
+      <c r="P63" s="3" t="n"/>
+      <c r="Q63" s="3" t="n"/>
     </row>
     <row r="64" ht="27" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
@@ -11549,11 +10605,7 @@
           <t>{"efficiency": 1.6, "deviationRisk": 0.045}</t>
         </is>
       </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K64" s="3" t="n"/>
       <c r="L64" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "ship_performance", "base": 0.32, "operation": "add_percent", "stackGroup": "ship_performance", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.04}, {"effectId": "space_stability", "base": 0.26, "operation": "add_percent", "stackGroup": "space_stability", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.035}, {"effectId": "void_ship_range", "base": 0.22, "operation": "add_percent", "stackGroup": "void_ship_range", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.06}]</t>
@@ -11569,21 +10621,9 @@
           <t>{"predecessorId": "method.zhoutian_craft.5", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P64" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q64" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O64" s="3" t="n"/>
+      <c r="P64" s="3" t="n"/>
+      <c r="Q64" s="3" t="n"/>
     </row>
     <row r="65" ht="27" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
@@ -11632,11 +10672,7 @@
           <t>{"efficiency": 1.72, "deviationRisk": 0.04}</t>
         </is>
       </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K65" s="3" t="n"/>
       <c r="L65" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "artifact_power", "base": 0.5, "operation": "add_percent", "stackGroup": "artifact_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.045}, {"effectId": "cave_heaven_growth", "base": 0.25, "operation": "add_percent", "stackGroup": "cave_heaven_growth", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.035}, {"effectId": "dao_artifact_stability", "base": 0.25, "operation": "add_percent", "stackGroup": "dao_artifact_stability", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.07}]</t>
@@ -11652,21 +10688,9 @@
           <t>{"predecessorId": "method.zhoutian_craft.6", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P65" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q65" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O65" s="3" t="n"/>
+      <c r="P65" s="3" t="n"/>
+      <c r="Q65" s="3" t="n"/>
     </row>
     <row r="66" ht="27" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
@@ -11715,11 +10739,7 @@
           <t>{"efficiency": 1.84, "deviationRisk": 0.035}</t>
         </is>
       </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K66" s="3" t="n"/>
       <c r="L66" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "world_artifact_power", "base": 0.45, "operation": "add_percent", "stackGroup": "world_artifact_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.05}, {"effectId": "formation_power", "base": 0.46, "operation": "add_percent", "stackGroup": "formation_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.045}, {"effectId": "star_array_output", "base": 0.28, "operation": "add_percent", "stackGroup": "star_array_output", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.08}]</t>
@@ -11735,21 +10755,9 @@
           <t>{"predecessorId": "method.zhoutian_craft.7", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q66" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O66" s="3" t="n"/>
+      <c r="P66" s="3" t="n"/>
+      <c r="Q66" s="3" t="n"/>
     </row>
     <row r="67" ht="27" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
@@ -11794,11 +10802,7 @@
           <t>{"efficiency": 1.96, "deviationRisk": 0.03}</t>
         </is>
       </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K67" s="3" t="n"/>
       <c r="L67" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "immortal_artifact_power", "base": 0.55, "operation": "add_percent", "stackGroup": "immortal_artifact_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.055}, {"effectId": "tribulation_control", "base": 0.36, "operation": "add_percent", "stackGroup": "tribulation_control", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.045}, {"effectId": "artifact_tribulation_success", "base": 0.3, "operation": "add_percent", "stackGroup": "artifact_tribulation_success", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "production", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.09}]</t>
@@ -11814,21 +10818,9 @@
           <t>{"predecessorId": "method.zhoutian_craft.8", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q67" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O67" s="3" t="n"/>
+      <c r="P67" s="3" t="n"/>
+      <c r="Q67" s="3" t="n"/>
     </row>
     <row r="68" ht="27" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
@@ -11873,11 +10865,7 @@
           <t>{"efficiency": 0.96, "deviationRisk": 0.075}</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K68" s="3" t="n"/>
       <c r="L68" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "gather_yield", "base": 0.11, "operation": "add_percent", "stackGroup": "gather_yield", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.018}, {"effectId": "exploration_safety", "base": 0.074, "operation": "add_percent", "stackGroup": "exploration_safety", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.014}, {"effectId": "gather_speed", "base": 0.092, "operation": "add_percent", "stackGroup": "gather_speed", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.028}]</t>
@@ -11889,21 +10877,9 @@
         </is>
       </c>
       <c r="N68" s="3" t="n"/>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P68" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q68" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O68" s="3" t="n"/>
+      <c r="P68" s="3" t="n"/>
+      <c r="Q68" s="3" t="n"/>
     </row>
     <row r="69" ht="27" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
@@ -11952,11 +10928,7 @@
           <t>{"efficiency": 1.08, "deviationRisk": 0.07}</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K69" s="3" t="n"/>
       <c r="L69" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "trade_profit", "base": 0.11, "operation": "add_percent", "stackGroup": "trade_profit", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "governance", "target": "faction", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.018}, {"effectId": "beast_power", "base": 0.147, "operation": "add_percent", "stackGroup": "beast_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "governance", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.023}, {"effectId": "beast_contract_capacity", "base": 0.92, "operation": "add_flat", "stackGroup": "beast_contract_capacity", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "control", "target": "controlled_entity", "polarity": "positive", "valueType": "flat", "displayPriority": 3}, "masteryGrowth": 0.92}]</t>
@@ -11972,21 +10944,9 @@
           <t>{"predecessorId": "method.wanxiang.1", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O69" s="3" t="n"/>
+      <c r="P69" s="3" t="n"/>
+      <c r="Q69" s="3" t="n"/>
     </row>
     <row r="70" ht="27" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
@@ -12035,11 +10995,7 @@
           <t>{"efficiency": 1.2, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K70" s="3" t="n"/>
       <c r="L70" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "rare_find_chance", "base": 0.147, "operation": "add_percent", "stackGroup": "rare_find_chance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.023}, {"effectId": "beast_growth", "base": 0.129, "operation": "add_percent", "stackGroup": "beast_growth", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "governance", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.02}, {"effectId": "spirit_vein_detection", "base": 0.147, "operation": "add_percent", "stackGroup": "spirit_vein_detection", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.046}]</t>
@@ -12055,21 +11011,9 @@
           <t>{"predecessorId": "method.wanxiang.2", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P70" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q70" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O70" s="3" t="n"/>
+      <c r="P70" s="3" t="n"/>
+      <c r="Q70" s="3" t="n"/>
     </row>
     <row r="71" ht="27" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
@@ -12118,11 +11062,7 @@
           <t>{"efficiency": 1.32, "deviationRisk": 0.06}</t>
         </is>
       </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K71" s="3" t="n"/>
       <c r="L71" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "exploration_safety", "base": 0.202, "operation": "add_percent", "stackGroup": "exploration_safety", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.028}, {"effectId": "rare_find_chance", "base": 0.184, "operation": "add_percent", "stackGroup": "rare_find_chance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.028}, {"effectId": "weather_warning", "base": 0.166, "operation": "add_percent", "stackGroup": "weather_warning", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.046}]</t>
@@ -12138,21 +11078,9 @@
           <t>{"predecessorId": "method.wanxiang.3", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P71" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q71" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O71" s="3" t="n"/>
+      <c r="P71" s="3" t="n"/>
+      <c r="Q71" s="3" t="n"/>
     </row>
     <row r="72" ht="27" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
@@ -12201,11 +11129,7 @@
           <t>{"efficiency": 1.44, "deviationRisk": 0.055}</t>
         </is>
       </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K72" s="3" t="n"/>
       <c r="L72" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "travel_efficiency", "base": 0.276, "operation": "add_percent", "stackGroup": "travel_efficiency", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.032}, {"effectId": "lilian_capacity", "base": 0.166, "operation": "add_percent", "stackGroup": "lilian_capacity", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.023}, {"effectId": "route_discovery", "base": 0.202, "operation": "add_percent", "stackGroup": "route_discovery", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.055}]</t>
@@ -12221,21 +11145,9 @@
           <t>{"predecessorId": "method.wanxiang.4", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P72" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q72" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O72" s="3" t="n"/>
+      <c r="P72" s="3" t="n"/>
+      <c r="Q72" s="3" t="n"/>
     </row>
     <row r="73" ht="27" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
@@ -12284,11 +11196,7 @@
           <t>{"efficiency": 1.56, "deviationRisk": 0.05}</t>
         </is>
       </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K73" s="3" t="n"/>
       <c r="L73" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "void_survival", "base": 0.313, "operation": "add_percent", "stackGroup": "void_survival", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.037}, {"effectId": "ship_performance", "base": 0.147, "operation": "add_percent", "stackGroup": "ship_performance", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "controlled_entity", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.023}, {"effectId": "void_route_safety", "base": 0.202, "operation": "add_percent", "stackGroup": "void_route_safety", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.055}]</t>
@@ -12304,21 +11212,9 @@
           <t>{"predecessorId": "method.wanxiang.5", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q73" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O73" s="3" t="n"/>
+      <c r="P73" s="3" t="n"/>
+      <c r="Q73" s="3" t="n"/>
     </row>
     <row r="74" ht="27" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
@@ -12367,11 +11263,7 @@
           <t>{"efficiency": 1.68, "deviationRisk": 0.045}</t>
         </is>
       </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K74" s="3" t="n"/>
       <c r="L74" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "settlement_output", "base": 0.258, "operation": "add_percent", "stackGroup": "settlement_output", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "governance", "target": "faction", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.032}, {"effectId": "trade_profit", "base": 0.221, "operation": "add_percent", "stackGroup": "trade_profit", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "governance", "target": "faction", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.028}, {"effectId": "governance_efficiency", "base": 0.23, "operation": "add_percent", "stackGroup": "governance_efficiency", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "governance", "target": "faction", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.064}]</t>
@@ -12387,21 +11279,9 @@
           <t>{"predecessorId": "method.wanxiang.6", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P74" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q74" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O74" s="3" t="n"/>
+      <c r="P74" s="3" t="n"/>
+      <c r="Q74" s="3" t="n"/>
     </row>
     <row r="75" ht="27" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
@@ -12450,11 +11330,7 @@
           <t>{"efficiency": 1.8, "deviationRisk": 0.04}</t>
         </is>
       </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K75" s="3" t="n"/>
       <c r="L75" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "world_growth", "base": 0.313, "operation": "add_percent", "stackGroup": "world_growth", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "governance", "target": "world", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.037}, {"effectId": "settlement_output", "base": 0.331, "operation": "add_percent", "stackGroup": "settlement_output", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "governance", "target": "faction", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.037}, {"effectId": "world_ecology_stability", "base": 0.258, "operation": "add_percent", "stackGroup": "world_ecology_stability", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "governance", "target": "world", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.074}]</t>
@@ -12470,21 +11346,9 @@
           <t>{"predecessorId": "method.wanxiang.7", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O75" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P75" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q75" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O75" s="3" t="n"/>
+      <c r="P75" s="3" t="n"/>
+      <c r="Q75" s="3" t="n"/>
     </row>
     <row r="76" ht="27" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
@@ -12529,11 +11393,7 @@
           <t>{"efficiency": 1.92, "deviationRisk": 0.035}</t>
         </is>
       </c>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K76" s="3" t="n"/>
       <c r="L76" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "ascension_route_stability", "base": 0.414, "operation": "add_percent", "stackGroup": "ascension_route_stability", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "world", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.046}, {"effectId": "lilian_capacity", "base": 0.322, "operation": "add_percent", "stackGroup": "lilian_capacity", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.037}, {"effectId": "ascension_route_capacity", "base": 0.92, "operation": "add_flat", "stackGroup": "ascension_route_capacity", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "exploration", "target": "world", "polarity": "positive", "valueType": "flat", "displayPriority": 3}, "masteryGrowth": 0.92}]</t>
@@ -12549,21 +11409,9 @@
           <t>{"predecessorId": "method.wanxiang.8", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O76" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P76" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q76" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O76" s="3" t="n"/>
+      <c r="P76" s="3" t="n"/>
+      <c r="Q76" s="3" t="n"/>
     </row>
     <row r="77" ht="27" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
@@ -12608,14 +11456,10 @@
           <t>{"efficiency": 1.52, "deviationRisk": 0.045}</t>
         </is>
       </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K77" s="3" t="n"/>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"tribulation_forecast","base":0.198,"operation":"add_percent","stackGroup":"tribulation_forecast","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.033},{"effectId":"karma_resistance","base":0.132,"operation":"add_percent","stackGroup":"karma_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.024},{"effectId":"tribulation_warning_time","base":0.198,"operation":"add_percent","stackGroup":"tribulation_warning_time","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"exploration","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.055}]</t>
+          <t>[{"effectId": "tribulation_forecast", "base": 0.198, "operation": "add_percent", "stackGroup": "tribulation_forecast", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.033}, {"effectId": "karma_resistance", "base": 0.132, "operation": "add_percent", "stackGroup": "karma_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.024}, {"effectId": "tribulation_warning_time", "base": 0.198, "operation": "add_percent", "stackGroup": "tribulation_warning_time", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.055}]</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -12624,21 +11468,9 @@
         </is>
       </c>
       <c r="N77" s="3" t="n"/>
-      <c r="O77" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P77" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q77" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O77" s="3" t="n"/>
+      <c r="P77" s="3" t="n"/>
+      <c r="Q77" s="3" t="n"/>
     </row>
     <row r="78" ht="27" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
@@ -12687,14 +11519,10 @@
           <t>{"efficiency": 1.64, "deviationRisk": 0.04}</t>
         </is>
       </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K78" s="3" t="n"/>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"law_resistance","base":0.22,"operation":"add_percent","stackGroup":"law_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.033},{"effectId":"tribulation_forecast","base":0.308,"operation":"add_percent","stackGroup":"tribulation_forecast","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.039},{"effectId":"law_seed_growth","base":0.242,"operation":"add_percent","stackGroup":"law_seed_growth","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.066}]</t>
+          <t>[{"effectId": "law_resistance", "base": 0.22, "operation": "add_percent", "stackGroup": "law_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.033}, {"effectId": "tribulation_forecast", "base": 0.308, "operation": "add_percent", "stackGroup": "tribulation_forecast", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.039}, {"effectId": "law_seed_growth", "base": 0.242, "operation": "add_percent", "stackGroup": "law_seed_growth", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.066}]</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -12707,21 +11535,9 @@
           <t>{"predecessorId": "method.jiuji.1", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O78" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P78" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q78" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O78" s="3" t="n"/>
+      <c r="P78" s="3" t="n"/>
+      <c r="Q78" s="3" t="n"/>
     </row>
     <row r="79" ht="27" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
@@ -12770,14 +11586,10 @@
           <t>{"efficiency": 1.76, "deviationRisk": 0.035}</t>
         </is>
       </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K79" s="3" t="n"/>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"law_resistance","base":0.374,"operation":"add_percent","stackGroup":"law_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.044},{"effectId":"tribulation_control","base":0.198,"operation":"add_percent","stackGroup":"tribulation_control","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"control","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.031},{"effectId":"tribulation_plan_slots","base":1.1,"operation":"add_flat","stackGroup":"tribulation_plan_slots","stackPolicy":"highest","activation":"active_method","attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"flat","displayPriority":3},"masteryGrowth":1.1}]</t>
+          <t>[{"effectId": "law_resistance", "base": 0.374, "operation": "add_percent", "stackGroup": "law_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.044}, {"effectId": "tribulation_control", "base": 0.198, "operation": "add_percent", "stackGroup": "tribulation_control", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.031}, {"effectId": "tribulation_plan_slots", "base": 1.1, "operation": "add_flat", "stackGroup": "tribulation_plan_slots", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 3}, "masteryGrowth": 1.1}]</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -12790,21 +11602,9 @@
           <t>{"predecessorId": "method.jiuji.2", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O79" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P79" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q79" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O79" s="3" t="n"/>
+      <c r="P79" s="3" t="n"/>
+      <c r="Q79" s="3" t="n"/>
     </row>
     <row r="80" ht="27" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
@@ -12853,14 +11653,10 @@
           <t>{"efficiency": 1.88, "deviationRisk": 0.03}</t>
         </is>
       </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K80" s="3" t="n"/>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"tribulation_resistance","base":0.352,"operation":"add_percent","stackGroup":"tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.044},{"effectId":"heart_tribulation_resistance","base":0.33,"operation":"add_percent","stackGroup":"heart_tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.044},{"effectId":"tribulation_resource_efficiency","base":0.308,"operation":"add_percent","stackGroup":"tribulation_resource_efficiency","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.088}]</t>
+          <t>[{"effectId": "tribulation_resistance", "base": 0.352, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.044}, {"effectId": "heart_tribulation_resistance", "base": 0.33, "operation": "add_percent", "stackGroup": "heart_tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.044}, {"effectId": "tribulation_resource_efficiency", "base": 0.308, "operation": "add_percent", "stackGroup": "tribulation_resource_efficiency", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.088}]</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -12873,21 +11669,9 @@
           <t>{"predecessorId": "method.jiuji.3", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O80" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P80" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q80" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O80" s="3" t="n"/>
+      <c r="P80" s="3" t="n"/>
+      <c r="Q80" s="3" t="n"/>
     </row>
     <row r="81" ht="27" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
@@ -12932,14 +11716,10 @@
           <t>{"efficiency": 2, "deviationRisk": 0.025}</t>
         </is>
       </c>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K81" s="3" t="n"/>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId":"tribulation_resistance","base":0.55,"operation":"add_percent","stackGroup":"tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.055},{"effectId":"ascension_success","base":0.264,"operation":"add_percent","stackGroup":"ascension_success","stackPolicy":"add_capped","activation":"active_method","cap":0.75,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.039},{"effectId":"ascension_failure_protection","base":0.22,"operation":"add_percent","stackGroup":"ascension_failure_protection","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.066}]</t>
+          <t>[{"effectId": "tribulation_resistance", "base": 0.55, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.055}, {"effectId": "ascension_success", "base": 0.264, "operation": "add_percent", "stackGroup": "ascension_success", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.039}, {"effectId": "ascension_failure_protection", "base": 0.22, "operation": "add_percent", "stackGroup": "ascension_failure_protection", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "dujie", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.066}]</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -12952,21 +11732,9 @@
           <t>{"predecessorId": "method.jiuji.4", "predecessorMastery": 0.8}</t>
         </is>
       </c>
-      <c r="O81" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P81" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q81" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O81" s="3" t="n"/>
+      <c r="P81" s="3" t="n"/>
+      <c r="Q81" s="3" t="n"/>
     </row>
     <row r="82" ht="27" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
@@ -13007,11 +11775,7 @@
           <t>{"efficiency": 1.2, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K82" s="3" t="n"/>
       <c r="L82" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "melee_damage", "base": 0.35, "operation": "add_percent", "stackGroup": "melee_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 1.2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.11}, {"effectId": "health_cost", "base": 0.11, "operation": "add_percent", "stackGroup": "health_cost", "stackPolicy": "unique", "activation": "active_method", "cap": 0.35, "attributes": {"category": "survival", "target": "self", "polarity": "negative", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.074}, {"effectId": "low_health_damage", "base": 0.276, "operation": "add_percent", "stackGroup": "low_health_damage", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.092}]</t>
@@ -13023,21 +11787,9 @@
         </is>
       </c>
       <c r="N82" s="3" t="n"/>
-      <c r="O82" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P82" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q82" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O82" s="3" t="n"/>
+      <c r="P82" s="3" t="n"/>
+      <c r="Q82" s="3" t="n"/>
     </row>
     <row r="83" ht="27" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
@@ -13078,11 +11830,7 @@
           <t>{"efficiency": 1.08, "deviationRisk": 0.07}</t>
         </is>
       </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K83" s="3" t="n"/>
       <c r="L83" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "travel_efficiency", "base": 0.258, "operation": "add_percent", "stackGroup": "travel_efficiency", "stackPolicy": "highest", "activation": "active_method", "cap": 1.5, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.092}, {"effectId": "escape_success", "base": 0.184, "operation": "add_percent", "stackGroup": "escape_success", "stackPolicy": "highest", "activation": "active_method", "cap": 0.75, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.092}]</t>
@@ -13094,21 +11842,9 @@
         </is>
       </c>
       <c r="N83" s="3" t="n"/>
-      <c r="O83" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P83" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q83" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O83" s="3" t="n"/>
+      <c r="P83" s="3" t="n"/>
+      <c r="Q83" s="3" t="n"/>
     </row>
     <row r="84" ht="27" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
@@ -13149,11 +11885,7 @@
           <t>{"efficiency": 1.2, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K84" s="3" t="n"/>
       <c r="L84" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "poison_power", "base": 0.294, "operation": "add_percent", "stackGroup": "poison_power", "stackPolicy": "highest", "activation": "active_method", "cap": 1.5, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.11}, {"effectId": "poison_resistance", "base": 0.221, "operation": "add_percent", "stackGroup": "poison_resistance", "stackPolicy": "highest", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.092}, {"effectId": "poison_duration", "base": 0.184, "operation": "add_percent", "stackGroup": "poison_duration", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.074}]</t>
@@ -13165,21 +11897,9 @@
         </is>
       </c>
       <c r="N84" s="3" t="n"/>
-      <c r="O84" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P84" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q84" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O84" s="3" t="n"/>
+      <c r="P84" s="3" t="n"/>
+      <c r="Q84" s="3" t="n"/>
     </row>
     <row r="85" ht="27" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
@@ -13220,11 +11940,7 @@
           <t>{"efficiency": 1.08, "deviationRisk": 0.07}</t>
         </is>
       </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K85" s="3" t="n"/>
       <c r="L85" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "rare_find_chance", "base": 0.166, "operation": "add_percent", "stackGroup": "rare_find_chance", "stackPolicy": "highest", "activation": "active_method", "cap": 0.75, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.074}, {"effectId": "exploration_safety", "base": 0.147, "operation": "add_percent", "stackGroup": "exploration_safety", "stackPolicy": "highest", "activation": "active_method", "cap": 1.5, "attributes": {"category": "utility", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.074}, {"effectId": "danger_warning", "base": 0.166, "operation": "add_percent", "stackGroup": "danger_warning", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.055}]</t>
@@ -13236,21 +11952,9 @@
         </is>
       </c>
       <c r="N85" s="3" t="n"/>
-      <c r="O85" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P85" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q85" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O85" s="3" t="n"/>
+      <c r="P85" s="3" t="n"/>
+      <c r="Q85" s="3" t="n"/>
     </row>
     <row r="86" ht="27" customHeight="1">
       <c r="A86" s="3" t="inlineStr">
@@ -13291,11 +11995,7 @@
           <t>{"efficiency": 1.2, "deviationRisk": 0.065}</t>
         </is>
       </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K86" s="3" t="n"/>
       <c r="L86" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "talisman_capacity", "base": 2.76, "operation": "add_flat", "stackGroup": "talisman_capacity", "stackPolicy": "highest", "activation": "active_method", "cap": 99, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 1}, "masteryGrowth": 1.84}, {"effectId": "activation_speed", "base": 0.221, "operation": "add_percent", "stackGroup": "activation_speed", "stackPolicy": "highest", "activation": "active_method", "cap": 1.5, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.092}, {"effectId": "talisman_cost_efficiency", "base": 0.166, "operation": "add_percent", "stackGroup": "talisman_cost_efficiency", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "production", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.055}]</t>
@@ -13307,21 +12007,9 @@
         </is>
       </c>
       <c r="N86" s="3" t="n"/>
-      <c r="O86" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P86" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q86" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O86" s="3" t="n"/>
+      <c r="P86" s="3" t="n"/>
+      <c r="Q86" s="3" t="n"/>
     </row>
     <row r="87" ht="27" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
@@ -13362,11 +12050,7 @@
           <t>{"efficiency": 1.08, "deviationRisk": 0.07}</t>
         </is>
       </c>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="K87" s="3" t="n"/>
       <c r="L87" s="3" t="inlineStr">
         <is>
           <t>[{"effectId": "melee_damage", "base": 0.276, "operation": "add_percent", "stackGroup": "melee_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 1.2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.11}, {"effectId": "armor_pierce", "base": 0.166, "operation": "add_percent", "stackGroup": "armor_pierce", "stackPolicy": "highest", "activation": "active_method", "cap": 0.9, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.074}, {"effectId": "stagger_power", "base": 0.221, "operation": "add_percent", "stackGroup": "stagger_power", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.074}]</t>
@@ -13378,21 +12062,9 @@
         </is>
       </c>
       <c r="N87" s="3" t="n"/>
-      <c r="O87" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P87" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q87" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="O87" s="3" t="n"/>
+      <c r="P87" s="3" t="n"/>
+      <c r="Q87" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
